--- a/important_spreadsheets/region_coordinates_per_participant.xlsx
+++ b/important_spreadsheets/region_coordinates_per_participant.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emory\Documents\git_projects\Research\bug_identification\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emory\Documents\git_projects\Research\bug_identification\important_spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59159DF-3451-463B-B147-3EB03DD23929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256236F2-4509-4A7F-BD73-7736C21FD3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B158B9D7-F826-4185-925C-4FE09A0904E0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{B158B9D7-F826-4185-925C-4FE09A0904E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2820" uniqueCount="513">
   <si>
     <t>session</t>
   </si>
@@ -834,6 +834,747 @@
   </si>
   <si>
     <t>p8_stonefly</t>
+  </si>
+  <si>
+    <t>p12_ladybug_a</t>
+  </si>
+  <si>
+    <t>p12_ladybug</t>
+  </si>
+  <si>
+    <t>p12</t>
+  </si>
+  <si>
+    <t>5:02</t>
+  </si>
+  <si>
+    <t>(355,70)</t>
+  </si>
+  <si>
+    <t>(355,825)</t>
+  </si>
+  <si>
+    <t>5:29</t>
+  </si>
+  <si>
+    <t>(1248, 825)</t>
+  </si>
+  <si>
+    <t>(1248,70)</t>
+  </si>
+  <si>
+    <t>p12_ladybug_b</t>
+  </si>
+  <si>
+    <t>p12_ladybug_c</t>
+  </si>
+  <si>
+    <t>(829,825)</t>
+  </si>
+  <si>
+    <t>(829, 70)</t>
+  </si>
+  <si>
+    <t>p12_stonefly_a</t>
+  </si>
+  <si>
+    <t>p12_stonefly</t>
+  </si>
+  <si>
+    <t>(829,820)</t>
+  </si>
+  <si>
+    <t>(829,70)</t>
+  </si>
+  <si>
+    <t>2:59</t>
+  </si>
+  <si>
+    <t>p12_stonefly_b</t>
+  </si>
+  <si>
+    <t>(960,755)</t>
+  </si>
+  <si>
+    <t>(960,70)</t>
+  </si>
+  <si>
+    <t>(0,755)</t>
+  </si>
+  <si>
+    <t>11:38</t>
+  </si>
+  <si>
+    <t>p12_silverfish_a</t>
+  </si>
+  <si>
+    <t>p12_silverfish</t>
+  </si>
+  <si>
+    <t>(1085,755)</t>
+  </si>
+  <si>
+    <t>(1085,70)</t>
+  </si>
+  <si>
+    <t>15:13</t>
+  </si>
+  <si>
+    <t>(785,755)</t>
+  </si>
+  <si>
+    <t>(785,70)</t>
+  </si>
+  <si>
+    <t>p12_silverfish_b</t>
+  </si>
+  <si>
+    <t>p12_silverfish_c</t>
+  </si>
+  <si>
+    <t>(1100,755)</t>
+  </si>
+  <si>
+    <t>(1100,70)</t>
+  </si>
+  <si>
+    <t>p13_ladybug</t>
+  </si>
+  <si>
+    <t>p13</t>
+  </si>
+  <si>
+    <t>(300,755)</t>
+  </si>
+  <si>
+    <t>(300,70)</t>
+  </si>
+  <si>
+    <t>(300, 755)</t>
+  </si>
+  <si>
+    <t>p13_silverfish</t>
+  </si>
+  <si>
+    <t>p13_praying_mantis</t>
+  </si>
+  <si>
+    <t>p13_weevil</t>
+  </si>
+  <si>
+    <t>p14_ladybug</t>
+  </si>
+  <si>
+    <t>p14</t>
+  </si>
+  <si>
+    <t>3:29</t>
+  </si>
+  <si>
+    <t>p14_ladybug_a</t>
+  </si>
+  <si>
+    <t>p14_ladybug_b</t>
+  </si>
+  <si>
+    <t>(780,710)</t>
+  </si>
+  <si>
+    <t>(780,70)</t>
+  </si>
+  <si>
+    <t>(0,710)</t>
+  </si>
+  <si>
+    <t>p14_stonefly</t>
+  </si>
+  <si>
+    <t>p14_silverfish</t>
+  </si>
+  <si>
+    <t>2:45</t>
+  </si>
+  <si>
+    <t>p15_ladybug</t>
+  </si>
+  <si>
+    <t>p15</t>
+  </si>
+  <si>
+    <t>(400,826)</t>
+  </si>
+  <si>
+    <t>(400,70)</t>
+  </si>
+  <si>
+    <t>(1920,826)</t>
+  </si>
+  <si>
+    <t>(0,826)</t>
+  </si>
+  <si>
+    <t>p15_ladybug_a</t>
+  </si>
+  <si>
+    <t>p15_ladybug_b</t>
+  </si>
+  <si>
+    <t>(738,770)</t>
+  </si>
+  <si>
+    <t>(738,70)</t>
+  </si>
+  <si>
+    <t>(0,770)</t>
+  </si>
+  <si>
+    <t>1:33</t>
+  </si>
+  <si>
+    <t>p15_stonefly_a</t>
+  </si>
+  <si>
+    <t>p15_stonefly</t>
+  </si>
+  <si>
+    <t>(800,770)</t>
+  </si>
+  <si>
+    <t>(800,70)</t>
+  </si>
+  <si>
+    <t>p15_stonefly_b</t>
+  </si>
+  <si>
+    <t>p15_praying_mantis</t>
+  </si>
+  <si>
+    <t>(855,723)</t>
+  </si>
+  <si>
+    <t>(855,70)</t>
+  </si>
+  <si>
+    <t>2:47</t>
+  </si>
+  <si>
+    <t>p15_spider</t>
+  </si>
+  <si>
+    <t>(800,780)</t>
+  </si>
+  <si>
+    <t>(0,780)</t>
+  </si>
+  <si>
+    <t>12:01</t>
+  </si>
+  <si>
+    <t>(855,780)</t>
+  </si>
+  <si>
+    <t>p15_spider_a</t>
+  </si>
+  <si>
+    <t>p15_spider_b</t>
+  </si>
+  <si>
+    <t>12:23</t>
+  </si>
+  <si>
+    <t>p15_spider_c</t>
+  </si>
+  <si>
+    <t>(855,660)</t>
+  </si>
+  <si>
+    <t>(1920,660)</t>
+  </si>
+  <si>
+    <t>(0,660)</t>
+  </si>
+  <si>
+    <t>p15_spider_d</t>
+  </si>
+  <si>
+    <t>(855,890)</t>
+  </si>
+  <si>
+    <t>(1920,890)</t>
+  </si>
+  <si>
+    <t>(0,890)</t>
+  </si>
+  <si>
+    <t>p15_weevil</t>
+  </si>
+  <si>
+    <t>p16_ladybug_1</t>
+  </si>
+  <si>
+    <t>p16</t>
+  </si>
+  <si>
+    <t>(300,870)</t>
+  </si>
+  <si>
+    <t>(1920,870)</t>
+  </si>
+  <si>
+    <t>(0,870)</t>
+  </si>
+  <si>
+    <t>p16_ladybug_2</t>
+  </si>
+  <si>
+    <t>0:06</t>
+  </si>
+  <si>
+    <t>p16_ladybug_2_a</t>
+  </si>
+  <si>
+    <t>p16_ladybug_2_b</t>
+  </si>
+  <si>
+    <t>(1100,870)</t>
+  </si>
+  <si>
+    <t>p16_ladybug_3</t>
+  </si>
+  <si>
+    <t>p16_ladybug_3_a</t>
+  </si>
+  <si>
+    <t>0:36</t>
+  </si>
+  <si>
+    <t>p16_ladybug_3_b</t>
+  </si>
+  <si>
+    <t>(1035,870)</t>
+  </si>
+  <si>
+    <t>(1035,70)</t>
+  </si>
+  <si>
+    <t>p16_ladybug_4</t>
+  </si>
+  <si>
+    <t>3:15</t>
+  </si>
+  <si>
+    <t>p16_stonefly_1</t>
+  </si>
+  <si>
+    <t>p16_stonefly_1_a</t>
+  </si>
+  <si>
+    <t>p16_stonefly_1_b</t>
+  </si>
+  <si>
+    <t>(300,735)</t>
+  </si>
+  <si>
+    <t>(1100,735)</t>
+  </si>
+  <si>
+    <t>(1920,735)</t>
+  </si>
+  <si>
+    <t>(0,735)</t>
+  </si>
+  <si>
+    <t>p16_stonefly_2</t>
+  </si>
+  <si>
+    <t>AI_code</t>
+  </si>
+  <si>
+    <t>p16_stonefly_3</t>
+  </si>
+  <si>
+    <t>p16_firefly</t>
+  </si>
+  <si>
+    <t>(300,728)</t>
+  </si>
+  <si>
+    <t>(1920,728)</t>
+  </si>
+  <si>
+    <t>(0,728)</t>
+  </si>
+  <si>
+    <t>p16_praying_mantis_1</t>
+  </si>
+  <si>
+    <t>1:29</t>
+  </si>
+  <si>
+    <t>p16_praying_mantis_1_a</t>
+  </si>
+  <si>
+    <t>p16_praying_mantis_1_b</t>
+  </si>
+  <si>
+    <t>(1100,728)</t>
+  </si>
+  <si>
+    <t>(1100, 728)</t>
+  </si>
+  <si>
+    <t>p16_praying_mantis_2</t>
+  </si>
+  <si>
+    <t>p16_praying_mantis_3</t>
+  </si>
+  <si>
+    <t>p16_spider</t>
+  </si>
+  <si>
+    <t>(840,728)</t>
+  </si>
+  <si>
+    <t>AI_report</t>
+  </si>
+  <si>
+    <t>p16_weevil_1</t>
+  </si>
+  <si>
+    <t>p16_weevil_2</t>
+  </si>
+  <si>
+    <t>p17_ladybug</t>
+  </si>
+  <si>
+    <t>p17_ladybug_a</t>
+  </si>
+  <si>
+    <t>p17</t>
+  </si>
+  <si>
+    <t>1:50</t>
+  </si>
+  <si>
+    <t>(305,70)</t>
+  </si>
+  <si>
+    <t>(305,735)</t>
+  </si>
+  <si>
+    <t>p17_ladybug_b</t>
+  </si>
+  <si>
+    <t>5:17</t>
+  </si>
+  <si>
+    <t>(950,735)</t>
+  </si>
+  <si>
+    <t>(950,70)</t>
+  </si>
+  <si>
+    <t>7:08</t>
+  </si>
+  <si>
+    <t>(290,735)</t>
+  </si>
+  <si>
+    <t>(290,70)</t>
+  </si>
+  <si>
+    <t>(750,735)</t>
+  </si>
+  <si>
+    <t>(750,70)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the code part on the left side is actually 2 code windows </t>
+  </si>
+  <si>
+    <t>p17_ladybug_c</t>
+  </si>
+  <si>
+    <t>p17_ladybug_d</t>
+  </si>
+  <si>
+    <t>(215,735)</t>
+  </si>
+  <si>
+    <t>(215,70)</t>
+  </si>
+  <si>
+    <t>(1200,735)</t>
+  </si>
+  <si>
+    <t>(1200,70)</t>
+  </si>
+  <si>
+    <t>p17_stonefly</t>
+  </si>
+  <si>
+    <t>(380,730)</t>
+  </si>
+  <si>
+    <t>(380,70)</t>
+  </si>
+  <si>
+    <t>(0,730)</t>
+  </si>
+  <si>
+    <t>p17_spider</t>
+  </si>
+  <si>
+    <t>p17_praying_mantis</t>
+  </si>
+  <si>
+    <t>p17_weevil</t>
+  </si>
+  <si>
+    <t>p18_ladybug_a</t>
+  </si>
+  <si>
+    <t>p18_ladybug</t>
+  </si>
+  <si>
+    <t>p18</t>
+  </si>
+  <si>
+    <t>2:22</t>
+  </si>
+  <si>
+    <t>(312,780)</t>
+  </si>
+  <si>
+    <t>(312,70)</t>
+  </si>
+  <si>
+    <t>11:23</t>
+  </si>
+  <si>
+    <t>(505,790)</t>
+  </si>
+  <si>
+    <t>(505,70)</t>
+  </si>
+  <si>
+    <t>(1920,790)</t>
+  </si>
+  <si>
+    <t>(0,790)</t>
+  </si>
+  <si>
+    <t>p18_ladybug_b</t>
+  </si>
+  <si>
+    <t>p18_ladybug_c</t>
+  </si>
+  <si>
+    <t>(505,710)</t>
+  </si>
+  <si>
+    <t>p18_stonefly</t>
+  </si>
+  <si>
+    <t>5:50</t>
+  </si>
+  <si>
+    <t>(505,720)</t>
+  </si>
+  <si>
+    <t>(0,720)</t>
+  </si>
+  <si>
+    <t>p18_stonefly_a</t>
+  </si>
+  <si>
+    <t>p18_stonefly_b</t>
+  </si>
+  <si>
+    <t>(505,550)</t>
+  </si>
+  <si>
+    <t>(0,550)</t>
+  </si>
+  <si>
+    <t>(505,1080)</t>
+  </si>
+  <si>
+    <t>16:09</t>
+  </si>
+  <si>
+    <t>p18_silverfish_a</t>
+  </si>
+  <si>
+    <t>p18_silverfish</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>(740,550)</t>
+  </si>
+  <si>
+    <t>(740,1080)</t>
+  </si>
+  <si>
+    <t>p18_silverfish_b</t>
+  </si>
+  <si>
+    <t>p18_silverfish_c</t>
+  </si>
+  <si>
+    <t>(580,550)</t>
+  </si>
+  <si>
+    <t>(580,70)</t>
+  </si>
+  <si>
+    <t>(580,1080)</t>
+  </si>
+  <si>
+    <t>p18_spider_a</t>
+  </si>
+  <si>
+    <t>p18_spider</t>
+  </si>
+  <si>
+    <t>10:03</t>
+  </si>
+  <si>
+    <t>p18_spider_b</t>
+  </si>
+  <si>
+    <t>(700,550)</t>
+  </si>
+  <si>
+    <t>(700,70)</t>
+  </si>
+  <si>
+    <t>(700,1080)</t>
+  </si>
+  <si>
+    <t>p19_ladybug_1</t>
+  </si>
+  <si>
+    <t>p19</t>
+  </si>
+  <si>
+    <t>(330,800)</t>
+  </si>
+  <si>
+    <t>(330,70)</t>
+  </si>
+  <si>
+    <t>(1920,800)</t>
+  </si>
+  <si>
+    <t>(0,800)</t>
+  </si>
+  <si>
+    <t>p19_ladybug_2</t>
+  </si>
+  <si>
+    <t>p19_stonefly</t>
+  </si>
+  <si>
+    <t>p19_silverfish</t>
+  </si>
+  <si>
+    <t>p19_spider</t>
+  </si>
+  <si>
+    <t>p19_firefly</t>
+  </si>
+  <si>
+    <t>p19_hornet</t>
+  </si>
+  <si>
+    <t>p19_weevil</t>
+  </si>
+  <si>
+    <t>p19_praying_mantis</t>
+  </si>
+  <si>
+    <t>p20_ladybug_1</t>
+  </si>
+  <si>
+    <t>p20</t>
+  </si>
+  <si>
+    <t>(390,840)</t>
+  </si>
+  <si>
+    <t>(390,70)</t>
+  </si>
+  <si>
+    <t>(1920,840)</t>
+  </si>
+  <si>
+    <t>(0,840)</t>
+  </si>
+  <si>
+    <t>p20_ladybug_2</t>
+  </si>
+  <si>
+    <t>0:55</t>
+  </si>
+  <si>
+    <t>(640,840)</t>
+  </si>
+  <si>
+    <t>(640,70)</t>
+  </si>
+  <si>
+    <t>p20_ladybug_3</t>
+  </si>
+  <si>
+    <t>p20_stonefly_1</t>
+  </si>
+  <si>
+    <t>p20_stonefly_2</t>
+  </si>
+  <si>
+    <t>p20_spider</t>
+  </si>
+  <si>
+    <t>p21</t>
+  </si>
+  <si>
+    <t>p21_stonefly_1</t>
+  </si>
+  <si>
+    <t>(330,750)</t>
+  </si>
+  <si>
+    <t>p21_stonefly_2</t>
+  </si>
+  <si>
+    <t>p21_hornet</t>
+  </si>
+  <si>
+    <t>(350,750)</t>
+  </si>
+  <si>
+    <t>(350,70)</t>
+  </si>
+  <si>
+    <t>p21_spider</t>
+  </si>
+  <si>
+    <t>p20_ladybug_4</t>
+  </si>
+  <si>
+    <t>p20_ladybug_3_b</t>
+  </si>
+  <si>
+    <t>p20_ladybug_3_a</t>
+  </si>
+  <si>
+    <t>p13_stonefly_1</t>
+  </si>
+  <si>
+    <t>p13_stonefly_2</t>
   </si>
 </sst>
 </file>
@@ -1199,10 +1940,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFFB6D4B-C3DC-47F1-9675-1A93E6AEDFDB}">
-  <dimension ref="A1:W65"/>
+  <dimension ref="A1:W150"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="1" max="1" width="26.85546875" customWidth="1"/>
     <col min="2" max="2" width="27.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.28515625" style="1" customWidth="1"/>
     <col min="4" max="7" width="12.85546875" style="1" customWidth="1"/>
@@ -5031,6 +5772,4952 @@
         <v>23</v>
       </c>
     </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q66" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P67" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P69" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q69" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q71" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="R71" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P72" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q72" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="R72" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q73" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="R73" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P74" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q74" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="R74" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P75" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q75" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="R75" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P76" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q76" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="R76" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P77" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q77" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="R77" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P78" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q78" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="R78" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P79" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q79" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="R79" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N80" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P80" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q80" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="R80" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P81" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q81" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="R81" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P82" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q82" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="R82" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="N83" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P83" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q83" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="R83" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="O84" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P84" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q84" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="R84" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="N85" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P85" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q85" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="R85" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P86" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q86" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="R86" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="N87" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P87" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q87" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="R87" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="N88" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P88" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q88" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="R88" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P89" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q89" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="R89" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="N90" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P90" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q90" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="R90" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P91" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q91" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="R91" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P92" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q92" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="R92" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P93" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q93" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="R93" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P94" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q94" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="R94" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P95" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q95" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="R95" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="O96" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P96" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q96" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="R96" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="S96" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T96" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U96" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="V96" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="O97" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P97" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q97" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="R97" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="S97" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T97" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U97" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="V97" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="O98" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P98" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q98" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="R98" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="S98" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T98" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U98" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="V98" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M99" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="O99" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P99" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q99" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="R99" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="S99" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T99" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U99" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="V99" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M100" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="O100" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P100" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q100" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="R100" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="S100" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T100" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U100" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="V100" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M101" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="O101" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P101" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q101" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="R101" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="S101" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T101" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U101" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="V101" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N102" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="O102" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P102" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q102" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="R102" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="S102" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T102" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="U102" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="V102" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M103" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P103" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q103" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="R103" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="S103" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T103" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="U103" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="V103" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M104" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N104" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="O104" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P104" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q104" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="R104" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M105" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N105" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="O105" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P105" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q105" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="R105" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="O106" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P106" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q106" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="R106" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="S106" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T106" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="U106" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="V106" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M107" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N107" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P107" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q107" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="R107" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="S107" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T107" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="U107" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="V107" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M108" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="O108" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P108" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q108" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="R108" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="S108" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T108" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="U108" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="V108" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M109" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N109" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="O109" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P109" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q109" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="R109" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="S109" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T109" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="U109" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="V109" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M110" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N110" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="O110" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q110" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="R110" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M111" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N111" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="O111" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P111" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q111" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="R111" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="112" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M112" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="N112" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="O112" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P112" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q112" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="R112" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M113" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="N113" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="O113" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P113" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q113" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="R113" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="S113" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T113" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U113" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="V113" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M114" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="N114" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="O114" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P114" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q114" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="R114" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="S114" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T114" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U114" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="V114" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W114" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M115" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="N115" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P115" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q115" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="R115" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="S115" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T115" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U115" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="V115" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W115" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="N116" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P116" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q116" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="R116" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M117" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="N117" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O117" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P117" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q117" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="R117" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M118" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="N118" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O118" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P118" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q118" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="R118" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M119" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="N119" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O119" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P119" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q119" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="R119" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M120" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="N120" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O120" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P120" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q120" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="R120" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M121" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="O121" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P121" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q121" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="R121" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="N122" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O122" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P122" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q122" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="R122" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="N123" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="O123" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P123" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q123" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="R123" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L124" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M124" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="N124" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O124" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P124" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q124" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="R124" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L125" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M125" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="N125" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O125" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P125" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q125" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="R125" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M126" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="N126" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O126" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P126" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q126" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="R126" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M127" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="N127" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O127" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P127" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q127" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="R127" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M128" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="N128" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O128" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P128" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q128" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="R128" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L129" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M129" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="N129" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O129" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P129" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q129" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="R129" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L130" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M130" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="N130" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="O130" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P130" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q130" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="R130" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L131" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M131" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="N131" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="O131" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P131" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q131" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="R131" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L132" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M132" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="N132" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="O132" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P132" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q132" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="R132" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L133" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M133" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="N133" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="O133" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P133" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q133" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="R133" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M134" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="N134" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="O134" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P134" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q134" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="R134" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L135" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M135" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="N135" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="O135" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P135" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q135" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="R135" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L136" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M136" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="N136" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="O136" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P136" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q136" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="R136" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L137" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M137" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="N137" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="O137" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P137" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q137" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="R137" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L138" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M138" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="N138" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="O138" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P138" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q138" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="R138" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L139" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M139" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="N139" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="O139" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P139" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q139" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="R139" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L140" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M140" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="N140" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="O140" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P140" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q140" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="R140" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="K141" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L141" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M141" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="N141" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="O141" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P141" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q141" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="R141" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="K142" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L142" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M142" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="N142" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="O142" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P142" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q142" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="R142" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="K143" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L143" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M143" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="N143" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="O143" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P143" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q143" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="R143" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="K144" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L144" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M144" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="N144" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="O144" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P144" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q144" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="R144" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="K145" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L145" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M145" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="N145" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="O145" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P145" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q145" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="R145" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="K146" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L146" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M146" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="N146" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="O146" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P146" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q146" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="R146" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="K147" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L147" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M147" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="N147" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O147" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P147" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q147" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="R147" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="K148" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L148" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M148" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="N148" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O148" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P148" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q148" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="R148" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="K149" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L149" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M149" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="N149" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O149" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P149" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q149" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="R149" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J150" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="K150" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L150" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M150" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="N150" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O150" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P150" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q150" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="R150" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
